--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="117">
   <si>
     <t>Profile</t>
   </si>
@@ -146,22 +146,40 @@
     <t>LOINC#89016-0</t>
   </si>
   <si>
+    <t>LOINC#89018-6</t>
+  </si>
+  <si>
+    <t>LOINC#89020-2</t>
+  </si>
+  <si>
+    <t>LOINC#89022-8</t>
+  </si>
+  <si>
+    <t>LOINC#89026-9</t>
+  </si>
+  <si>
+    <t>LOINC#89028-5</t>
+  </si>
+  <si>
+    <t>LOINC#89025-1</t>
+  </si>
+  <si>
     <t>LOINC#89017-8</t>
   </si>
   <si>
-    <t>LOINC#89018-6</t>
-  </si>
-  <si>
-    <t>LOINC#89028-5</t>
-  </si>
-  <si>
-    <t>LOINC#89020-2</t>
-  </si>
-  <si>
     <t>LOINC#89019-4</t>
   </si>
   <si>
-    <t>LOINC#89022-8</t>
+    <t>LOINC#89021-0</t>
+  </si>
+  <si>
+    <t>LOINC#89023-6</t>
+  </si>
+  <si>
+    <t>LOINC#89027-7</t>
+  </si>
+  <si>
+    <t>LOINC#89029-3</t>
   </si>
   <si>
     <t>TWHA-LabResult-General</t>
@@ -478,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1323,28 +1341,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F25" t="s" s="2">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1358,28 +1376,28 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1393,10 +1411,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>14</v>
@@ -1405,16 +1423,16 @@
         <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1428,28 +1446,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -1466,7 +1484,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1475,7 +1493,7 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>14</v>
@@ -1484,7 +1502,7 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1498,10 +1516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1510,16 +1528,16 @@
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1533,13 +1551,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>14</v>
@@ -1548,13 +1566,13 @@
         <v>14</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1568,28 +1586,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>39</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -1603,10 +1621,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>14</v>
@@ -1615,16 +1633,16 @@
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1638,28 +1656,28 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -1673,25 +1691,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>17</v>
@@ -1708,28 +1726,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -1746,7 +1764,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>14</v>
@@ -1755,7 +1773,7 @@
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>14</v>
@@ -1764,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>18</v>
@@ -1778,10 +1796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>14</v>
@@ -1790,16 +1808,16 @@
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
@@ -1816,7 +1834,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>14</v>
@@ -1825,7 +1843,7 @@
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>14</v>
@@ -1834,7 +1852,7 @@
         <v>14</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -1848,28 +1866,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -1883,28 +1901,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
@@ -1918,28 +1936,28 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -1956,7 +1974,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>14</v>
@@ -1965,7 +1983,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>14</v>
@@ -1974,7 +1992,7 @@
         <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -1991,7 +2009,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2000,7 +2018,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>14</v>
@@ -2009,7 +2027,7 @@
         <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2026,7 +2044,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>14</v>
@@ -2035,7 +2053,7 @@
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>14</v>
@@ -2058,28 +2076,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2093,28 +2111,28 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2128,10 +2146,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2140,16 +2158,16 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2166,33 +2184,243 @@
         <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="C49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s" s="2">
+      <c r="F51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="F49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H49" t="s" s="2">
+      <c r="D52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K49" t="s" s="2">
+      <c r="G52" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -116,7 +116,7 @@
     <t>健康檢查健康管理分級 Observation Profile</t>
   </si>
   <si>
-    <t>SNOMED CT#371607000</t>
+    <t>SNOMED CT#406221003</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -209,7 +209,7 @@
     <t>臨場健康服務發現問題/風險 Profile</t>
   </si>
   <si>
-    <t>SNOMED CT#278486003</t>
+    <t>SNOMED CT#17458004</t>
   </si>
   <si>
     <t>CodeableConcept, string</t>
@@ -320,19 +320,19 @@
     <t>視力與辨色力檢查 Profile</t>
   </si>
   <si>
-    <t>LOINC#79880-1</t>
-  </si>
-  <si>
-    <t>LOINC#70936-0</t>
+    <t>LOINC#98497-1</t>
+  </si>
+  <si>
+    <t>LOINC#98498-9</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept</t>
   </si>
   <si>
-    <t>LOINC#70935-2</t>
-  </si>
-  <si>
-    <t>LOINC#48024-3</t>
+    <t>LOINC#98499-7</t>
+  </si>
+  <si>
+    <t>LOINC#46673-0</t>
   </si>
   <si>
     <t>TWHA-VitalSigns</t>
@@ -353,13 +353,13 @@
     <t>特別危害健康作業危害因子暴露史 Profile</t>
   </si>
   <si>
-    <t>LOINC#74213-0</t>
-  </si>
-  <si>
-    <t>LOINC#74212-2</t>
-  </si>
-  <si>
-    <t>LOINC#80436-9</t>
+    <t>LOINC#87729-0</t>
+  </si>
+  <si>
+    <t>LOINC#104905-5</t>
+  </si>
+  <si>
+    <t>LOINC#21847-9</t>
   </si>
   <si>
     <t>string</t>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -251,7 +251,7 @@
     <t>肺功能檢查 Profile</t>
   </si>
   <si>
-    <t>LOINC#19876-2</t>
+    <t>LOINC#19868-9</t>
   </si>
   <si>
     <t>Quantityĵ</t>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -281,19 +281,19 @@
     <t>嚼檳榔歷史與狀態 Profile</t>
   </si>
   <si>
-    <t>相關行為代碼系統#BetelNutChewing</t>
+    <t>【本地 stub】相關行為代碼系統（非權威定義）#BetelNutChewing</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
   <si>
-    <t>Betel Nut Chewing Behavior Code System#amount</t>
-  </si>
-  <si>
-    <t>Betel Nut Chewing Behavior Code System#year</t>
-  </si>
-  <si>
-    <t>Betel Nut Chewing Behavior Code System#quit</t>
+    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#amount</t>
+  </si>
+  <si>
+    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#year</t>
+  </si>
+  <si>
+    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#quit</t>
   </si>
   <si>
     <t>TWHA-SocialHistory-Sleep</t>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -281,19 +281,19 @@
     <t>嚼檳榔歷史與狀態 Profile</t>
   </si>
   <si>
-    <t>【本地 stub】相關行為代碼系統（非權威定義）#BetelNutChewing</t>
+    <t>相關行為代碼系統#BetelNutChewing</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
   <si>
-    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#amount</t>
-  </si>
-  <si>
-    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#year</t>
-  </si>
-  <si>
-    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）#quit</t>
+    <t>Betel Nut Chewing Behavior Code System#amount</t>
+  </si>
+  <si>
+    <t>Betel Nut Chewing Behavior Code System#year</t>
+  </si>
+  <si>
+    <t>Betel Nut Chewing Behavior Code System#quit</t>
   </si>
   <si>
     <t>TWHA-SocialHistory-Sleep</t>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="125">
   <si>
     <t>Profile</t>
   </si>
@@ -281,19 +281,43 @@
     <t>嚼檳榔歷史與狀態 Profile</t>
   </si>
   <si>
-    <t>相關行為代碼系統#BetelNutChewing</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
-    <t>Betel Nut Chewing Behavior Code System#amount</t>
-  </si>
-  <si>
-    <t>Betel Nut Chewing Behavior Code System#year</t>
-  </si>
-  <si>
-    <t>Betel Nut Chewing Behavior Code System#quit</t>
+    <t>SNOMED CT#698188003</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#amount</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#duration-years</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#cessation-duration</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#cessation-date</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#with-tobacco</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#additive</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#lime</t>
+  </si>
+  <si>
+    <t>LOINC#48766-0</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#hpa-category</t>
+  </si>
+  <si>
+    <t>嚼檳榔量化元件代碼系統#amount-coded</t>
   </si>
   <si>
     <t>TWHA-SocialHistory-Sleep</t>
@@ -496,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1957,7 +1981,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -1983,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>14</v>
@@ -1992,7 +2016,7 @@
         <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -2018,7 +2042,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>14</v>
@@ -2027,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2053,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>14</v>
@@ -2062,7 +2086,7 @@
         <v>14</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2076,28 +2100,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>42</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2111,28 +2135,28 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2146,10 +2170,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2158,16 +2182,16 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2184,7 +2208,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>14</v>
@@ -2193,7 +2217,7 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>14</v>
@@ -2202,7 +2226,7 @@
         <v>14</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>18</v>
@@ -2219,7 +2243,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2228,7 +2252,7 @@
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>14</v>
@@ -2237,7 +2261,7 @@
         <v>14</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>18</v>
@@ -2254,7 +2278,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2263,7 +2287,7 @@
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>14</v>
@@ -2286,28 +2310,28 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
@@ -2321,10 +2345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>69</v>
@@ -2333,7 +2357,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>14</v>
@@ -2342,7 +2366,7 @@
         <v>35</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2356,28 +2380,28 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
@@ -2391,36 +2415,281 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="C55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s" s="2">
+      <c r="I56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s" s="2">
+      <c r="B59" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="I55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K55" t="s" s="2">
+      <c r="C59" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -281,7 +281,7 @@
     <t>嚼檳榔歷史與狀態 Profile</t>
   </si>
   <si>
-    <t>SNOMED CT#698188003</t>
+    <t>嚼檳榔觀察項目代碼系統#betel-quid-chewing-status</t>
   </si>
   <si>
     <t>嚼檳榔量化元件代碼系統#amount</t>
